--- a/pricing/商务成品/对外/Trinity模型报价表.xlsx
+++ b/pricing/商务成品/对外/Trinity模型报价表.xlsx
@@ -624,42 +624,42 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>gpt-5.5</t>
+          <t>gpt-5-nano</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>6.2折</t>
+          <t>8.5折</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>6折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>5.5折</t>
+          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -668,42 +668,42 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>gpt-5.6-luna</t>
+          <t>gpt-5.3-codex</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.3 Codex</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>6.2折</t>
+          <t>8.5折</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>6折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>5.5折</t>
+          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -737,17 +737,17 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
+          <t>9.4折</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>9.2折</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
           <t>8.5折</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -756,42 +756,42 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>gpt-5-nano</t>
+          <t>gpt-5.1</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-5.1</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
+          <t>9.4折</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>9.2折</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
           <t>8.5折</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -800,42 +800,42 @@
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>gpt-5.1</t>
+          <t>gpt-5.2</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>GPT-5.1</t>
+          <t>GPT-5.2</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
+          <t>9.4折</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>9.2折</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
           <t>8.5折</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -844,42 +844,42 @@
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>gpt-5.2</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>GPT-5.2</t>
+          <t>GPT-5.4</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
+          <t>9.4折</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>9.2折</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
           <t>8.5折</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -888,42 +888,42 @@
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>gpt-5.3-codex</t>
+          <t>gpt-5.4-mini</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>GPT-5.3 Codex</t>
+          <t>GPT-5.4 Mini</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
+          <t>9.4折</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>9.2折</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
           <t>8.5折</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -932,42 +932,42 @@
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>gpt-5.4</t>
+          <t>gpt-5.4-nano</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>GPT-5.4</t>
+          <t>GPT-5.4 nano</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
+          <t>9.4折</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>9.2折</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
           <t>8.5折</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -976,42 +976,42 @@
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>gpt-5.4-mini</t>
+          <t>gpt-5.4-pro</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>GPT-5.4 Mini</t>
+          <t>GPT-5.4 Pro</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>180.00</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
+          <t>9.4折</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>9.2折</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
           <t>8.5折</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -1020,42 +1020,42 @@
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>gpt-5.4-nano</t>
+          <t>gpt-5.5</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>GPT-5.4 nano</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
+          <t>9.4折</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>9.2折</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
           <t>8.5折</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -1064,42 +1064,42 @@
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>gpt-5.4-pro</t>
+          <t>gpt-5.6-luna</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>GPT-5.4 Pro</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>180.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
+          <t>9.4折</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>9.2折</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
           <t>8.5折</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -1133,23 +1133,23 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
+          <t>9.4折</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>9.2折</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
           <t>8.5折</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>7.2折</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
-      <c r="B15" s="7" t="n"/>
+      <c r="B15" s="6" t="n"/>
       <c r="C15" s="4" t="inlineStr">
         <is>
           <t>gpt-5.6-terra</t>
@@ -1177,35 +1177,31 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
+          <t>9.4折</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>9.2折</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
           <t>8.5折</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>7.2折</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+      <c r="B16" s="6" t="n"/>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>claude-fable-5</t>
+          <t>gpt-6-astra</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Claude Fable 5</t>
+          <t>GPT-6 Astra</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1225,7 +1221,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9.4折</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1235,7 +1231,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>8.5折</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1240,12 @@
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>gpt-image-2</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Claude Opus 4.6</t>
+          <t>GPT Image 2</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1259,17 +1255,17 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9.4折</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1279,7 +1275,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>8.5折</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1284,12 @@
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>gpt-image-2.5-flare</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Claude Opus 4.7</t>
+          <t>GPT Image 2.5 Flare</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1303,17 +1299,17 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9.4折</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1323,21 +1319,21 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>8.5折</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="n"/>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>claude-opus-4-8</t>
+          <t>gpt-image-2.5-sunburst</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Claude Opus 4.8</t>
+          <t>GPT Image 2.5 Sunburst</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1347,17 +1343,17 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9.4折</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1367,36 +1363,40 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>8.5折</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>claude-opus-5</t>
+          <t>claude-fable-5</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Claude Opus 5</t>
+          <t>Claude Fable 5</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1420,27 +1420,27 @@
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Claude Sonnet 4.6</t>
+          <t>Claude Opus 4.6</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1461,30 +1461,30 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
-      <c r="B22" s="7" t="n"/>
+      <c r="B22" s="6" t="n"/>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>claude-sonnet-5</t>
+          <t>claude-opus-4-7</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Claude Sonnet 5</t>
+          <t>Claude Opus 4.7</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -1505,49 +1505,45 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
+      <c r="B23" s="6" t="n"/>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Flash</t>
+          <t>Claude Opus 4.8</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
+          <t>9.5折</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
           <t>9.2折</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>8.8折</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>7.8折</t>
         </is>
       </c>
     </row>
@@ -1556,42 +1552,42 @@
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite</t>
+          <t>claude-opus-5</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Flash Lite</t>
+          <t>Claude Opus 5</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
+          <t>9.5折</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
           <t>9.2折</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>8.8折</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>7.8折</t>
         </is>
       </c>
     </row>
@@ -1600,110 +1596,114 @@
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>gemini-2.5-pro</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Pro</t>
+          <t>Claude Sonnet 4.6</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
+          <t>9.5折</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
           <t>9.2折</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>8.8折</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>7.8折</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
-      <c r="B26" s="6" t="n"/>
+      <c r="B26" s="7" t="n"/>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>gemini-3-flash-preview</t>
+          <t>claude-sonnet-5</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Gemini 3 Flash Preview</t>
+          <t>Claude Sonnet 5</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
+          <t>9.5折</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
           <t>9.2折</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>8.8折</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>7.8折</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
-      <c r="B27" s="6" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>gemini-3.1-flash-lite</t>
+          <t>gemini-2.5-flash</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Flash Lite</t>
+          <t>Gemini 2.5 Flash</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -1732,27 +1732,27 @@
       <c r="B28" s="6" t="n"/>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>gemini-3.1-pro-preview</t>
+          <t>gemini-2.5-flash-lite</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro Preview</t>
+          <t>Gemini 2.5 Flash Lite</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -1776,27 +1776,27 @@
       <c r="B29" s="6" t="n"/>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>gemini-3.1-pro-preview-customtools</t>
+          <t>gemini-2.5-pro</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro Preview Custom Tools</t>
+          <t>Gemini 2.5 Pro</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -1820,27 +1820,27 @@
       <c r="B30" s="6" t="n"/>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash</t>
+          <t>gemini-3-flash-preview</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3 Flash Preview</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -1864,27 +1864,27 @@
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>gemini-3.6-flash</t>
+          <t>gemini-3.1-flash-lite</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Gemini 3.6 Flash</t>
+          <t>Gemini 3.1 Flash Lite</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -1908,27 +1908,27 @@
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>gemini-3.7-flash</t>
+          <t>gemini-3.1-pro-preview</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Gemini 3.7 Flash</t>
+          <t>Gemini 3.1 Pro Preview</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -1952,134 +1952,130 @@
       <c r="B33" s="6" t="n"/>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash-lite</t>
+          <t>gemini-3.1-pro-preview-customtools</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash Lite</t>
+          <t>Gemini 3.1 Pro Preview Custom Tools</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>9折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>8.7折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
-      <c r="B34" s="7" t="n"/>
+      <c r="B34" s="6" t="n"/>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>gemini-3.8-flash</t>
+          <t>gemini-3.5-flash</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash</t>
+          <t>Gemini 3.5 Flash</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>9折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>8.7折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>DeepSeek</t>
-        </is>
-      </c>
+      <c r="B35" s="6" t="n"/>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>deepseek-v4-flash</t>
+          <t>gemini-3.6-flash</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash Direct</t>
+          <t>Gemini 3.6 Flash</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>7.6折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>6.7折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
@@ -2088,42 +2084,42 @@
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gemini-3.7-flash</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro Direct</t>
+          <t>Gemini 3.7 Flash</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>7.6折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>6.7折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
@@ -2132,114 +2128,110 @@
       <c r="B37" s="6" t="n"/>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>gemini-2.5-flash-image</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>DeepSeek V3.2</t>
+          <t>Gemini 2.5 Flash Image</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>9折</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>8.7折</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>8.2折</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
-      <c r="B38" s="7" t="n"/>
+      <c r="B38" s="6" t="n"/>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>deepseek-v4-flash-fast</t>
+          <t>gemini-3.1-flash-image</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash Fast</t>
+          <t>Gemini 3.1 Flash Image</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>9折</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>8.7折</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>8.2折</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>月之暗面</t>
-        </is>
-      </c>
+      <c r="B39" s="6" t="n"/>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>kimi-k2.7-code</t>
+          <t>gemini-3.1-flash-lite-image</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Kimi K2.7 Code</t>
+          <t>Gemini 3.1 Flash Lite Image</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -2249,46 +2241,46 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>9折</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>8.7折</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>8.2折</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
-      <c r="B40" s="7" t="n"/>
+      <c r="B40" s="6" t="n"/>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>kimi-k3</t>
+          <t>gemini-3.5-flash-lite</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Gemini 3.5 Flash Lite</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -2309,185 +2301,181 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>MiniMax</t>
-        </is>
-      </c>
+      <c r="B41" s="7" t="n"/>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>minimax-m2.5</t>
+          <t>gemini-3.8-flash</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>MiniMax M2.5</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>9折</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>8.7折</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>8.2折</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
-      <c r="B42" s="6" t="n"/>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>minimax-m2.7</t>
+          <t>deepseek-flash</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>MiniMax M2.7</t>
+          <t>DeepSeek Flash</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
-      <c r="B43" s="7" t="n"/>
+      <c r="B43" s="6" t="n"/>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>minimax-m3</t>
+          <t>deepseek-v4-flash</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>MiniMax M3</t>
+          <t>DeepSeek V4 Flash Direct</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>智谱</t>
-        </is>
-      </c>
+      <c r="B44" s="6" t="n"/>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>glm-5.2</t>
+          <t>deepseek-v4-flash-fast</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>GLM-5.2</t>
+          <t>DeepSeek V4 Flash Fast</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>6.2折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>6折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>5.5折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
@@ -2496,42 +2484,42 @@
       <c r="B45" s="6" t="n"/>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>glm-5.3</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>DeepSeek V4 Pro Direct</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>27.00</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
@@ -2540,27 +2528,27 @@
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>GLM-5.3-Flash</t>
+          <t>DeepSeek V3.2</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -2583,120 +2571,124 @@
       <c r="A47" s="6" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿里云·通义</t>
+          <t>月之暗面</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>qwen-flash</t>
+          <t>kimi-k2.7-code</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Qwen Flash</t>
+          <t>Kimi K2.7 Code</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>7.6折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>6.7折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
-      <c r="B48" s="6" t="n"/>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>qwen-max</t>
+          <t>kimi-k3</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Qwen Max</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>9.4折</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>7.6折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>6.7折</t>
+          <t>8.5折</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
-      <c r="B49" s="6" t="n"/>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>qwen-plus</t>
+          <t>minimax-m3</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Qwen Plus</t>
+          <t>MiniMax M3</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -2717,89 +2709,93 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
-      <c r="B50" s="6" t="n"/>
+      <c r="B50" s="7" t="n"/>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>qwen-turbo</t>
+          <t>minimax-m2.7</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Qwen Turbo</t>
+          <t>MiniMax M2.7</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
+          <t>8.5折</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
           <t>8.2折</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>7.6折</t>
-        </is>
-      </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>6.7折</t>
+          <t>7.2折</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
-      <c r="B51" s="6" t="n"/>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>智谱</t>
+        </is>
+      </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>qwen3.5-flash</t>
+          <t>glm-5.2</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Qwen3.5 Flash</t>
+          <t>GLM-5.2</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>6.2折</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>7.6折</t>
+          <t>6折</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>6.7折</t>
+          <t>5.5折</t>
         </is>
       </c>
     </row>
@@ -2808,66 +2804,66 @@
       <c r="B52" s="6" t="n"/>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>qwen3.5-plus</t>
+          <t>glm-5.3</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Qwen3.5 Plus</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>7.6折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>6.7折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
-      <c r="B53" s="6" t="n"/>
+      <c r="B53" s="7" t="n"/>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>qwen3.6-flash</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Qwen3.6 Flash</t>
+          <t>GLM-5.3-Flash</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -2877,46 +2873,50 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>7.6折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>6.7折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
-      <c r="B54" s="6" t="n"/>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>阿里云·通义</t>
+        </is>
+      </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>qwen3.6-plus</t>
+          <t>qwen3.6-flash</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Qwen3.6 Plus</t>
+          <t>Qwen3.6 Flash</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -2940,27 +2940,27 @@
       <c r="B55" s="6" t="n"/>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>qwen3.7-flash</t>
+          <t>qwen3.6-plus</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3.6 Plus</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -2984,27 +2984,27 @@
       <c r="B56" s="6" t="n"/>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>qwen3.7-max</t>
+          <t>qwen3.7-flash</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Qwen3.7 Max</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
@@ -3028,27 +3028,27 @@
       <c r="B57" s="6" t="n"/>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>qwen3.7-plus</t>
+          <t>qwen3.7-max</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Qwen3.7 Plus</t>
+          <t>Qwen3.7 Max</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -3069,30 +3069,30 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
-      <c r="B58" s="7" t="n"/>
+      <c r="B58" s="6" t="n"/>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>qwen3.8-max</t>
+          <t>qwen3.7-plus</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Qwen3.7 Plus</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
@@ -3113,19 +3113,15 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>GK</t>
-        </is>
-      </c>
+      <c r="B59" s="7" t="n"/>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>grok-4.5</t>
+          <t>qwen3.8-max</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Grok 4.5</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -3140,28 +3136,32 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>6.2折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>6折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>5.5折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
-      <c r="B60" s="7" t="n"/>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
           <t>grok-4.6</t>
@@ -3257,7 +3257,7 @@
           <t>生图</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
@@ -3289,40 +3289,36 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
+          <t>9.4折</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>9.2折</t>
+        </is>
+      </c>
+      <c r="J62" s="10" t="inlineStr">
+        <is>
           <t>8.5折</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="J62" s="10" t="inlineStr">
-        <is>
-          <t>7.2折</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n"/>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
+      <c r="B63" s="6" t="n"/>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-image</t>
+          <t>gpt-image-2.5-flare</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Flash Image</t>
+          <t>GPT Image 2.5 Flare</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>入 0.30 · 出 30.00</t>
+          <t>入 5.00 · 出 30.00 · 缓 1.25</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
@@ -3337,36 +3333,36 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>9折</t>
+          <t>9.4折</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>8.7折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>8.5折</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
-      <c r="B64" s="6" t="n"/>
+      <c r="B64" s="7" t="n"/>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>gemini-3.1-flash-image</t>
+          <t>gpt-image-2.5-sunburst</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Flash Image</t>
+          <t>GPT Image 2.5 Sunburst</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>入 0.50 · 出 60.00</t>
+          <t>入 5.00 · 出 30.00 · 缓 1.25</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
@@ -3381,36 +3377,40 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>9折</t>
+          <t>9.4折</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>8.7折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>8.5折</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n"/>
-      <c r="B65" s="7" t="n"/>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>gemini-3.1-flash-lite-image</t>
+          <t>gemini-2.5-flash-image</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Flash Lite Image</t>
+          <t>Gemini 2.5 Flash Image</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>入 0.25 · 出 30.00</t>
+          <t>入 0.30 · 出 30.00</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -3441,24 +3441,20 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="n"/>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>Vidu</t>
-        </is>
-      </c>
+      <c r="B66" s="6" t="n"/>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>viduq2-image</t>
+          <t>gemini-3.1-flash-image</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Vidu Q2 Image</t>
+          <t>Gemini 3.1 Flash Image</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>0.03（1K）</t>
+          <t>入 0.50 · 出 60.00</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -3473,40 +3469,36 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>7.5折</t>
+          <t>9折</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
-          <t>7折</t>
+          <t>8.7折</t>
         </is>
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>6.4折</t>
+          <t>8.2折</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n"/>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
+      <c r="B67" s="7" t="n"/>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>grok-imagine-image-pro</t>
+          <t>gemini-3.1-flash-lite-image</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Grok Imagine Image Pro</t>
+          <t>Gemini 3.1 Flash Lite Image</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>0.05（1K）</t>
+          <t>入 0.25 · 出 30.00</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -3521,36 +3513,40 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>6.2折</t>
+          <t>9折</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
         <is>
-          <t>6折</t>
+          <t>8.7折</t>
         </is>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>5.5折</t>
+          <t>8.2折</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n"/>
-      <c r="B68" s="7" t="n"/>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>Vidu</t>
+        </is>
+      </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>grok-imagine-image-quality</t>
+          <t>viduq2-image</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Grok Imagine Image Quality</t>
+          <t>Vidu Q2 Image</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>0.05（1K）</t>
+          <t>0.03（1K）</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -3565,17 +3561,17 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>6.2折</t>
+          <t>7.5折</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>6折</t>
+          <t>7折</t>
         </is>
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
-          <t>5.5折</t>
+          <t>6.4折</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3778,7 @@
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>3.50（480p）</t>
+          <t>1.40（480p）</t>
         </is>
       </c>
       <c r="F73" s="13" t="inlineStr">
@@ -3826,7 +3822,7 @@
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>5.60（480p）</t>
+          <t>4.20（480p）</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
@@ -3860,12 +3856,12 @@
       <c r="B75" s="6" t="n"/>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>seedance-2.0-os</t>
+          <t>seedance-2.0-overseas-hc-os</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Seedance 2.0</t>
+          <t>Seedance 2.0 Overseas HC</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
@@ -3904,17 +3900,17 @@
       <c r="B76" s="7" t="n"/>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>seedance-2.0-overseas-hc-os</t>
+          <t>seedance-2.5-overseas-hc-os</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Seedance 2.0 Overseas HC</t>
+          <t>Seedance 2.5 Overseas HC</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>7.00（480p）</t>
+          <t>10.70（480p）</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
@@ -3977,17 +3973,17 @@
       </c>
       <c r="H77" s="13" t="inlineStr">
         <is>
-          <t>9.8折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
-          <t>9.7折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J77" s="13" t="inlineStr">
         <is>
-          <t>9.4折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
@@ -4576,26 +4572,25 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B73:B76"/>
-    <mergeCell ref="B47:B58"/>
-    <mergeCell ref="A3:A61"/>
-    <mergeCell ref="B63:B65"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="A62:A68"/>
-    <mergeCell ref="B16:B22"/>
+  <mergeCells count="18">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B78:B85"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="B65:B67"/>
     <mergeCell ref="B69:B72"/>
     <mergeCell ref="B87:B90"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="B78:B85"/>
-    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B73:B76"/>
     <mergeCell ref="A69:A90"/>
-    <mergeCell ref="B3:B15"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="A3:A61"/>
+    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="B20:B26"/>
+    <mergeCell ref="B3:B19"/>
+    <mergeCell ref="B54:B59"/>
+    <mergeCell ref="B27:B41"/>
+    <mergeCell ref="A62:A68"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
